--- a/DOSSIES_MULTIFORMATO/SEJEL/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEJEL/dossie.xlsx
@@ -628,12 +628,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2018NE00339</t>
+          <t>2018NE00334</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26/2015</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8426.43</v>
+        <v>60372.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -651,19 +651,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>REFERENTE AO SEGUNDO TERMO ADITIVO AO CONTRATO Nº 026/2015 COM A EMPRESA PRODAM - PROCESSAMENTO DE DADOS AMAZONAS S/A, COM O OBJETO DE PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE WEBSITE.</t>
+          <t>REFERENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 006/2017 COM A EMPRESA PRODAM - PROCESSAMENTO DE DADOS AMAZONAS S/A, COM O OBJETO DE PRESTAÇÃO DE SERVIÇO DE REDE - INTERNET.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2018NE00334</t>
+          <t>2018NE00339</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>26/2015</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60372.9</v>
+        <v>8426.43</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>REFERENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 006/2017 COM A EMPRESA PRODAM - PROCESSAMENTO DE DADOS AMAZONAS S/A, COM O OBJETO DE PRESTAÇÃO DE SERVIÇO DE REDE - INTERNET.</t>
+          <t>REFERENTE AO SEGUNDO TERMO ADITIVO AO CONTRATO Nº 026/2015 COM A EMPRESA PRODAM - PROCESSAMENTO DE DADOS AMAZONAS S/A, COM O OBJETO DE PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE WEBSITE.</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2016NE00838</t>
+          <t>2016NE00837</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2202.92</v>
+        <v>925.5599999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 71 PARA AJUSTES ORÇAMENTÁRIO DE ENCERRAMENTO DE EXERCÍCIO.</t>
+          <t>ANULAÇÃO DA NE 27 PARA AJUSTES ORÇAMENTÁRIO DE ENCERRAMENTO DE EXERCÍCIO.</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2016NE00837</t>
+          <t>2016NE00838</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>925.5599999999999</v>
+        <v>2202.92</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -789,21 +789,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 27 PARA AJUSTES ORÇAMENTÁRIO DE ENCERRAMENTO DE EXERCÍCIO.</t>
+          <t>ANULAÇÃO DA NE 71 PARA AJUSTES ORÇAMENTÁRIO DE ENCERRAMENTO DE EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2016NE00523</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4/2012</t>
-        </is>
-      </c>
+          <t>2016NE00521</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>30/09/2016</t>
@@ -819,17 +815,21 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>CANCELAMENTO DE NE PARA ALTERAÇÃO NA MODALIDADE.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2016NE00521</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>2016NE00523</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4/2012</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>30/09/2016</t>
@@ -845,21 +845,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE NE PARA ALTERAÇÃO NA MODALIDADE.</t>
+          <t>SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2016NE00523</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4/2012</t>
-        </is>
-      </c>
+          <t>2016NE00521</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>30/09/2016</t>
@@ -875,17 +871,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>CANCELAMENTO DE NE PARA ALTERAÇÃO NA MODALIDADE.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2016NE00521</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>2016NE00523</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4/2012</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>30/09/2016</t>
@@ -901,7 +901,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE NE PARA ALTERAÇÃO NA MODALIDADE.</t>
+          <t>SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2016NE00366</t>
+          <t>2016NE00370</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE INFORMATICA EM GERAL, CONFORME O PROJETO BASICO</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL, CONFORME O PROJETO BÁSICO.</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2016NE00370</t>
+          <t>2016NE00366</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE INFORMÁTICA EM GERAL, CONFORME O PROJETO BÁSICO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA PARA PRESTAÇÃO DE SERVIÇOS DE INFORMATICA EM GERAL, CONFORME O PROJETO BASICO</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2018NE00591</t>
+          <t>2018NE00592</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>78.76000000000001</v>
+        <v>3589.74</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2018NE00592</t>
+          <t>2018NE00591</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3589.74</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2016NE00508</t>
+          <t>2016NE00519</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3870.79</v>
+        <v>3225.66</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1143,14 +1143,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRARAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTO</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2016NE00518</t>
+          <t>2016NE00510</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3225.66</v>
+        <v>3870.79</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1169,28 +1169,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CANNE PARA ALTERAÇÃO NA LICITAÇÃO.</t>
+          <t>CANNE PARA AJUSTES NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2016NE00511</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>4/2012</t>
-        </is>
-      </c>
+          <t>2016NE00510</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>28/09/2016</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3225.66</v>
+        <v>3870.79</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1199,14 +1195,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>CANNE PARA AJUSTES NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2016NE00519</t>
+          <t>2016NE00511</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1229,28 +1225,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTO</t>
+          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2016NE00508</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>4/2012</t>
-        </is>
-      </c>
+          <t>2016NE00518</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>28/09/2016</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3870.79</v>
+        <v>3225.66</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1259,24 +1251,28 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRARAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>CANNE PARA ALTERAÇÃO NA LICITAÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2016NE00518</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>2016NE00508</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4/2012</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>28/09/2016</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3225.66</v>
+        <v>3870.79</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1285,14 +1281,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CANNE PARA ALTERAÇÃO NA LICITAÇÃO.</t>
+          <t>SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRARAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2016NE00511</t>
+          <t>2016NE00519</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1315,24 +1311,28 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTO</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2016NE00510</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>2016NE00511</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4/2012</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>28/09/2016</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3870.79</v>
+        <v>3225.66</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1341,14 +1341,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CANNE PARA AJUSTES NA DESCRIÇÃO.</t>
+          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2016NE00510</t>
+          <t>2016NE00518</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3870.79</v>
+        <v>3225.66</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1367,14 +1367,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CANNE PARA AJUSTES NA DESCRIÇÃO.</t>
+          <t>CANNE PARA ALTERAÇÃO NA LICITAÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2016NE00519</t>
+          <t>2016NE00508</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3225.66</v>
+        <v>3870.79</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1397,14 +1397,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇOS DE PROCESSAMENTO DE DADOS, Descrição: SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTO</t>
+          <t>SERVIÇO ESPECIALIZADO EM CESSÃO DE USO DE PROGRARAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2019NE00313</t>
+          <t>2019NE00311</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1307.05</v>
+        <v>19.36</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2019NE00311</t>
+          <t>2019NE00313</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.36</v>
+        <v>1307.05</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1456,10 +1456,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2016NE00564</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>2016NE00565</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>18/2013</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>25/10/2016</t>
@@ -1475,21 +1479,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CANCELAR PARA AJUSTE ORÇAMENTARIO.</t>
+          <t>- TERMO DE CONTRATO Nº 018/2013 - TERCEIRO TERMO ADITIVO; - OBJETO: PRESTAÇÃO DE SERVIÇOS DE ACESSO À REDE DE INTERNET PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2016NE00565</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>18/2013</t>
-        </is>
-      </c>
+          <t>2016NE00564</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>25/10/2016</t>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>- TERMO DE CONTRATO Nº 018/2013 - TERCEIRO TERMO ADITIVO; - OBJETO: PRESTAÇÃO DE SERVIÇOS DE ACESSO À REDE DE INTERNET PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
+          <t>CANCELAR PARA AJUSTE ORÇAMENTARIO.</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2015NE00828</t>
+          <t>2015NE00821</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3517.65</v>
+        <v>485.46</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2015NE00834</t>
+          <t>2015NE00835</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1329.74</v>
+        <v>2590.92</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2015NE00835</t>
+          <t>2015NE00834</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2590.92</v>
+        <v>1329.74</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2015NE00821</t>
+          <t>2015NE00828</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>485.46</v>
+        <v>3517.65</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1646,14 +1646,10 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2017NE00221</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>6/2017</t>
-        </is>
-      </c>
+          <t>2017NE00227</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>20/04/2017</t>
@@ -1669,19 +1665,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ACESSO À REDE DE INTERNET PARA ATENDER AS NECESSIDADES DESTA SEJEL</t>
+          <t>ANULAÇÃO DE NE PARA ALTERAÇÃO NO CRONOGRAMA.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2017NE00228</t>
+          <t>2017NE00250</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1686,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>25874.1</v>
+        <v>2150.44</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1699,14 +1695,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ACESSO À INTERNET.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2017NE00225</t>
+          <t>2017NE00249</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1725,14 +1721,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>ANULAÇÃO DE EMPENHO PARA ALTERAÇÃO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2017NE00224</t>
+          <t>2017NE00251</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1751,7 +1747,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE PROCESSAMENTO DE DADOS (HOSPEDAGEM DE SITE).</t>
+          <t>ANULAÇÃO DE EMPRENHO PARA ALTERAÇÃO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1784,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2017NE00251</t>
+          <t>2017NE00224</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1807,14 +1803,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPRENHO PARA ALTERAÇÃO NA DESCRIÇÃO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE PROCESSAMENTO DE DADOS (HOSPEDAGEM DE SITE).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2017NE00249</t>
+          <t>2017NE00225</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1833,19 +1829,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO PARA ALTERAÇÃO NA DESCRIÇÃO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2017NE00250</t>
+          <t>2017NE00228</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1854,7 +1850,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2150.44</v>
+        <v>25874.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1863,17 +1859,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM CESSÃO DE USO DE PROGRAMA DE COMPUTAÇÃO PARA DISPONIBILIZAÇÃO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>SERVIÇOS DE ACESSO À INTERNET.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2017NE00227</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>2017NE00221</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>6/2017</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>20/04/2017</t>
@@ -1889,21 +1889,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE NE PARA ALTERAÇÃO NO CRONOGRAMA.</t>
+          <t>SERVIÇOS DE ACESSO À REDE DE INTERNET PARA ATENDER AS NECESSIDADES DESTA SEJEL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2017NE00053</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>26/2015</t>
-        </is>
-      </c>
+          <t>2017NE00056</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>20/01/2017</t>
@@ -1919,7 +1915,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE PROCESSAMENTO DE DADOS. (HOSPEDAGEM DE SITE)</t>
+          <t>CANCELAMENTO DO EMPENHO PARA ALTERAÇÃO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
@@ -1956,10 +1952,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2017NE00056</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>2017NE00053</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>26/2015</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>20/01/2017</t>
@@ -1975,14 +1975,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DO EMPENHO PARA ALTERAÇÃO NA DESCRIÇÃO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE PROCESSAMENTO DE DADOS. (HOSPEDAGEM DE SITE)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2017NE00676</t>
+          <t>2017NE00677</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>387.7</v>
+        <v>1728.09</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2017NE00677</t>
+          <t>2017NE00676</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1728.09</v>
+        <v>387.7</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2060,12 +2060,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2015NE00654</t>
+          <t>2015NE00659</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>26/2015</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3468.88</v>
+        <v>5830.92</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>Cobertura Financeira 2015.</t>
         </is>
       </c>
     </row>
@@ -2120,12 +2120,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2015NE00659</t>
+          <t>2015NE00654</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>26/2015</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5830.92</v>
+        <v>3468.88</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2143,19 +2143,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015.</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2020NE00056</t>
+          <t>2020NE00054</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4/2020</t>
+          <t>2/2020</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10204.74</v>
+        <v>53901.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Contrato 004/2020 - Gestor de Conteudo WEB</t>
+          <t>Contrato 002/2020 - Serviço de transmissão de dados</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020NE00054</t>
+          <t>2020NE00056</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2/2020</t>
+          <t>4/2020</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>53901.6</v>
+        <v>10204.74</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Contrato 002/2020 - Serviço de transmissão de dados</t>
+          <t>Contrato 004/2020 - Gestor de Conteudo WEB</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2018NE00135</t>
+          <t>2018NE00136</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>34498.8</v>
+        <v>8426.43</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2315,14 +2315,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA 132 PARA ACERTO NO ELEMENTO DE DESPESAS CONFORME PARECER DA INSPETORA DA SEFAZ.</t>
+          <t>ANULAÇÃO DA 134 PARA ACERTO NO ELEMENTO DE DESPESAS CONFORME PARECER DA INSPETORA DA SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2018NE00136</t>
+          <t>2018NE00135</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8426.43</v>
+        <v>34498.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2341,19 +2341,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA 134 PARA ACERTO NO ELEMENTO DE DESPESAS CONFORME PARECER DA INSPETORA DA SEFAZ.</t>
+          <t>ANULAÇÃO DA 132 PARA ACERTO NO ELEMENTO DE DESPESAS CONFORME PARECER DA INSPETORA DA SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2018NE00134</t>
+          <t>2018NE00132</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>26/2015</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>8426.43</v>
+        <v>34498.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2371,17 +2371,21 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SITE AS NECESSIDADES DESTA SECRETARIA</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE INTERNET ATRAVÉS DA REDE DO GOVERNO</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2018NE00131</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>2018NE00130</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>6/2017</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>05/03/2018</t>
@@ -2397,21 +2401,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ANULAR PARA ACERTO NA DESCRIÇÃO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE INTERNET ATRAVÉS DA REDE DO GOVERNO</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2018NE00130</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>6/2017</t>
-        </is>
-      </c>
+          <t>2018NE00131</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>05/03/2018</t>
@@ -2427,19 +2427,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE INTERNET ATRAVÉS DA REDE DO GOVERNO</t>
+          <t>ANULAR PARA ACERTO NA DESCRIÇÃO</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2018NE00132</t>
+          <t>2018NE00134</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>26/2015</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>34498.8</v>
+        <v>8426.43</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2457,19 +2457,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE INTERNET ATRAVÉS DA REDE DO GOVERNO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE HOSPEDAGEM DE SITE AS NECESSIDADES DESTA SECRETARIA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2015NE00003</t>
+          <t>2015NE00005</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18/2013</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>27028.23</v>
+        <v>2915.46</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2494,12 +2494,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2015NE00005</t>
+          <t>2015NE00003</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>18/2013</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2915.46</v>
+        <v>27028.23</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2524,10 +2524,14 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2016NE00040</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>2016NE00041</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>18/2014</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>04/01/2016</t>
@@ -2543,24 +2547,28 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ANULAR NE Nº 34 PARA AJUSTE NO VALOR GLOBAL CONFORME INSTRUÇÃO DO INSPETOR.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE´PROCESSAMENTO DE DADOS ATULIZAÇÃO DE WEB SITE</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2016NE00030</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>2016NE00034</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>26/2015</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5203.32</v>
+        <v>5176.02</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2569,19 +2577,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ANULAR NE 28 DE 04/01/2016 PARA MUDANÇA DE NATUREZA DE DESPESA CONFORME SOLICITAÇÃO DA CHEFE DO SETOR</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE PROCESSAMENTO DE DADOS ATUALIZAÇÃO DE WEB SITE.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2016NE00027</t>
+          <t>2016NE00028</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>26/2015</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2590,7 +2598,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5830.92</v>
+        <v>5203.32</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2599,19 +2607,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE DISPONIBILIDADE DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB) PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM HOSPEDAGEM DE SITE PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2016NE00033</t>
+          <t>2016NE00026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>26/2015</t>
+          <t>18/2013</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2620,7 +2628,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5203.32</v>
+        <v>42212.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2629,19 +2637,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADO EM PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SITE.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET) PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2016NE00026</t>
+          <t>2016NE00033</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>18/2013</t>
+          <t>26/2015</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2650,7 +2658,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>42212.4</v>
+        <v>5203.32</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2659,19 +2667,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇO DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET) PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADO EM PRESTAÇÃO DE SERVIÇO DE HOSPEDAGEM DE SITE.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2016NE00028</t>
+          <t>2016NE00027</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>26/2015</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2680,7 +2688,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5203.32</v>
+        <v>5830.92</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2689,28 +2697,24 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM HOSPEDAGEM DE SITE PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE DISPONIBILIDADE DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB) PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2016NE00034</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>26/2015</t>
-        </is>
-      </c>
+          <t>2016NE00030</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5176.02</v>
+        <v>5203.32</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2719,21 +2723,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇO DE PROCESSAMENTO DE DADOS ATUALIZAÇÃO DE WEB SITE.</t>
+          <t>ANULAR NE 28 DE 04/01/2016 PARA MUDANÇA DE NATUREZA DE DESPESA CONFORME SOLICITAÇÃO DA CHEFE DO SETOR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2016NE00041</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>18/2014</t>
-        </is>
-      </c>
+          <t>2016NE00040</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>04/01/2016</t>
@@ -2749,14 +2749,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE´PROCESSAMENTO DE DADOS ATULIZAÇÃO DE WEB SITE</t>
+          <t>ANULAR NE Nº 34 PARA AJUSTE NO VALOR GLOBAL CONFORME INSTRUÇÃO DO INSPETOR.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2019NE00252</t>
+          <t>2019NE00250</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2786,7 +2786,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2019NE00249</t>
+          <t>2019NE00251</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>erro de descrição</t>
+          <t>ERRO DE REFERENCIA</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2019NE00251</t>
+          <t>2019NE00249</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ERRO DE REFERENCIA</t>
+          <t>erro de descrição</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2019NE00250</t>
+          <t>2019NE00252</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2898,12 +2898,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2019NE00003</t>
+          <t>2019NE00004</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6/2017</t>
+          <t>26/2015</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>25874.1</v>
+        <v>3076.92</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2921,19 +2921,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS INTERNET ATRAVÉS DA REDE GOVERNO</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO E SERVIÇOS DE HOSPEDAGEM DE SITE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2019NE00004</t>
+          <t>2019NE00003</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>26/2015</t>
+          <t>6/2017</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3076.92</v>
+        <v>25874.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO E SERVIÇOS DE HOSPEDAGEM DE SITE</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS INTERNET ATRAVÉS DA REDE GOVERNO</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2014NE00017</t>
+          <t>2014NE00023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>18/2013</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5400</v>
+        <v>95715.17999999999</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3011,19 +3011,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Contrato No. 4/2012 - Sistema de Protocolo em Plataforma Web - SPROWEB</t>
+          <t>Contrato No. 18/2013 - Acesso Internet na velocidade 3Mbps</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2014NE00023</t>
+          <t>2014NE00017</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>18/2013</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>95715.17999999999</v>
+        <v>5400</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Contrato No. 18/2013 - Acesso Internet na velocidade 3Mbps</t>
+          <t>Contrato No. 4/2012 - Sistema de Protocolo em Plataforma Web - SPROWEB</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2015NE03019</t>
+          <t>2015NE00320</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>18/2013</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>59800.85</v>
+        <v>2915.46</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3127,14 +3127,14 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Empenho de contrato: importado manualmente em 21/09/2015</t>
+          <t>ANULAR PARA AJUSTER</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2015NE00342</t>
+          <t>2015NE00321</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3157,14 +3157,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>contrato 004/2012 - prodam segundo termo aditivo.</t>
+          <t>SEGUNDO TERMO ADITIVO AO CONTRATO 004/2012.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2015NE00318</t>
+          <t>2015NE00319</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ANULAR PARA AJUSTES.</t>
+          <t>Cobertura Financeira 2015 - De 04 a 11/2015</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2015NE00302</t>
+          <t>2015NE00341</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>18/2013</t>
+          <t>4/2012</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>59800.85</v>
+        <v>2915.46</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2º T.A AO CONTATRO 018/2013 - PRODAM/INTERNET.</t>
+          <t>cancelar para ajustes.</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2015NE00341</t>
+          <t>2015NE00302</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>18/2013</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2915.46</v>
+        <v>59800.85</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3277,14 +3277,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>cancelar para ajustes.</t>
+          <t>2º T.A AO CONTATRO 018/2013 - PRODAM/INTERNET.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2015NE00319</t>
+          <t>2015NE00318</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3307,14 +3307,14 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015 - De 04 a 11/2015</t>
+          <t>ANULAR PARA AJUSTES.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2015NE00321</t>
+          <t>2015NE00342</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3337,19 +3337,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SEGUNDO TERMO ADITIVO AO CONTRATO 004/2012.</t>
+          <t>contrato 004/2012 - prodam segundo termo aditivo.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2015NE00320</t>
+          <t>2015NE03019</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4/2012</t>
+          <t>18/2013</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2915.46</v>
+        <v>59800.85</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3367,19 +3367,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ANULAR PARA AJUSTER</t>
+          <t>Empenho de contrato: importado manualmente em 21/09/2015</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2016NE00071</t>
+          <t>2016NE00073</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>10/2014</t>
+          <t>24/2014</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>9238.32</v>
+        <v>21834</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3397,17 +3397,21 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO 010/2014 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS INFORMATICA DE FORMA EVENTUAL.</t>
+          <t>CONTRATO 024/2014 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET) PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2016NE00068</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>2016NE00065</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>10/2014</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
           <t>01/02/2016</t>
@@ -3423,21 +3427,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>anulação da ne 65 para acerto na descrição</t>
+          <t>TERMO DE CONTRATO 010/2014 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS INFORMATICA DE FORMA EVENTUAL.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2016NE00065</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>10/2014</t>
-        </is>
-      </c>
+          <t>2016NE00068</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
           <t>01/02/2016</t>
@@ -3453,19 +3453,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO 010/2014 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS INFORMATICA DE FORMA EVENTUAL.</t>
+          <t>anulação da ne 65 para acerto na descrição</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2016NE00073</t>
+          <t>2016NE00071</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>24/2014</t>
+          <t>10/2014</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>21834</v>
+        <v>9238.32</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CONTRATO 024/2014 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS DE ACESSO A REDE MUNDIAL DE COMPUTADORES (INTERNET) PARA ATENDER AS NECESSIDADES DESTA SEJEL.</t>
+          <t>TERMO DE CONTRATO 010/2014 - CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NA PRESTAÇÃO DE SERVIÇOS INFORMATICA DE FORMA EVENTUAL.</t>
         </is>
       </c>
     </row>
